--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23322,7 +23340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23366,6 +23384,194 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1978_79_0035 'ŽS Spišská Nová Ves' prev→CLUB_S1977_78_0032 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1978_79_0041 'TJ Baník Sokolov' prev→CLUB_S1977_78_0039 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1978_79_0084 'TJ Skloobal Nemšová' prev→CLUB_S1977_78_0508 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1978_79_0187 'Sokol Záluží (BER)' prev→CLUB_S1977_78_0149 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1978_79_0432 'Rájec – Jestřebí' prev→CLUB_S1977_78_0430 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1978_79_0025 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1978_79_0026 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1978_79_0027 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1978_79_0028 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1978_79_0103 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0009</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0009 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0010</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0010 'Kval o I.ČNHL sk. A' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0011</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0011 'Kval o I.ČNHL sk. B' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0017</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0017 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -36173,7 +36379,6 @@
         </is>
       </c>
     </row>
-    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -36772,7 +36977,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -40308,7 +40512,6 @@
         </is>
       </c>
     </row>
-    <row r="186"/>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
@@ -44173,7 +44376,6 @@
         </is>
       </c>
     </row>
-    <row r="274"/>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
@@ -46334,7 +46536,6 @@
         </is>
       </c>
     </row>
-    <row r="325"/>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
@@ -49525,7 +49726,6 @@
         </is>
       </c>
     </row>
-    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -52072,7 +52272,6 @@
         </is>
       </c>
     </row>
-    <row r="455"/>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
@@ -54310,7 +54509,6 @@
         </is>
       </c>
     </row>
-    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
@@ -55706,6 +55904,369 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0035</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0035 'ŽS Spišská Nová Ves' prev→CLUB_S1977_78_0032 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0041</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0041 'TJ Baník Sokolov' prev→CLUB_S1977_78_0039 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0084</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0084 'TJ Skloobal Nemšová' prev→CLUB_S1977_78_0508 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0187</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0187 'Sokol Záluží (BER)' prev→CLUB_S1977_78_0149 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0432</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0432 'Rájec – Jestřebí' prev→CLUB_S1977_78_0430 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0025</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0025 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0026</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0026 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0027</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0027 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0028</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0028 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0103</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0103 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0009</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1978_79_0009 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0010</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1978_79_0010 'Kval o I.ČNHL sk. A' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0011</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1978_79_0011 'Kval o I.ČNHL sk. B' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0017</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1978_79_0017 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14223,6 +14223,11 @@
           <t>CLUB_S1977_78_0427</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V60" t="inlineStr">
         <is>
           <t>TR_S1978_79_00340</t>
@@ -14268,6 +14273,11 @@
       <c r="R61" t="inlineStr">
         <is>
           <t>CLUB_S1977_78_0428</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -23340,7 +23350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23390,7 +23400,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1978_79_0035 'ŽS Spišská Nová Ves' prev→CLUB_S1977_78_0032 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -23402,7 +23412,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1978_79_0041 'TJ Baník Sokolov' prev→CLUB_S1977_78_0039 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23414,7 +23424,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1978_79_0084 'TJ Skloobal Nemšová' prev→CLUB_S1977_78_0508 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23426,7 +23436,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1978_79_0187 'Sokol Záluží (BER)' prev→CLUB_S1977_78_0149 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23438,7 +23448,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1978_79_0432 'Rájec – Jestřebí' prev→CLUB_S1977_78_0430 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23450,7 +23460,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1978_79_0025 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23462,7 +23472,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1978_79_0026 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23474,7 +23484,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1978_79_0027 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23486,7 +23496,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1978_79_0028 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23498,7 +23508,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1978_79_0103 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23508,14 +23518,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NODE_S1978_79_0009</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0009 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23525,14 +23530,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S1978_79_0010</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0010 'Kval o I.ČNHL sk. A' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23542,14 +23542,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S1978_79_0011</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0011 'Kval o I.ČNHL sk. B' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23559,17 +23554,456 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NODE_S1978_79_0017</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1978_79_0017 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Poruba' → 'HM Ostrava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -33017,12 +33451,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -33279,12 +33713,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -33368,12 +33802,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -33872,12 +34306,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -33998,12 +34432,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -34124,12 +34558,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity] || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -34502,12 +34936,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34722,12 +35156,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -34769,12 +35203,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -34806,12 +35240,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -34932,12 +35366,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -35100,12 +35534,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -35310,12 +35744,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -35399,12 +35833,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -35483,12 +35917,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -36379,6 +36813,7 @@
         </is>
       </c>
     </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -36977,6 +37412,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -37183,12 +37619,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -38011,12 +38447,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -39460,12 +39896,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Týnec nad Labem = TJ Metaz Týnec nL Labem (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín, district '(KOL)' potvrzen). **Metaz** = strojirensky podnik (drive Metaz Týnec nL Sázavou -&gt; nove pobocka v Kolinsku). NE Týnec nL Sázavou (Jawa motocykly, Benesov)! city Týnec nad Labem.</t>
+          <t>Týnec nad Labem = TJ Metaz Týnec nL Labem (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín, district '(KOL)' potvrzen). **Metaz** = strojirensky podnik (drive Metaz Týnec nL Sázavou -&gt; nove pobocka v Kolinsku). NE Týnec nL Sázavou (Jawa motocykly, Benesov)! city Týnec nad Labem. || TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Metaz Týnec nad Labem</t>
+          <t>Týnec nad Labem</t>
         </is>
       </c>
     </row>
@@ -40340,12 +40776,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Týnec nad Labem = TJ Metaz Týnec nL Labem (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín, district '(KOL)' potvrzen). **Metaz** = strojirensky podnik (drive Metaz Týnec nL Sázavou -&gt; nove pobocka v Kolinsku). NE Týnec nL Sázavou (Jawa motocykly, Benesov)! city Týnec nad Labem.</t>
+          <t>Týnec nad Labem = TJ Metaz Týnec nL Labem (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín, district '(KOL)' potvrzen). **Metaz** = strojirensky podnik (drive Metaz Týnec nL Sázavou -&gt; nove pobocka v Kolinsku). NE Týnec nL Sázavou (Jawa motocykly, Benesov)! city Týnec nad Labem. || TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Metaz Týnec nad Labem</t>
+          <t>Týnec nad Labem</t>
         </is>
       </c>
     </row>
@@ -40512,6 +40948,7 @@
         </is>
       </c>
     </row>
+    <row r="186"/>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
@@ -40545,12 +40982,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40765,12 +41202,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -41012,12 +41449,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -41578,12 +42015,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -41818,12 +42255,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -42006,12 +42443,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -43539,12 +43976,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -44376,6 +44813,7 @@
         </is>
       </c>
     </row>
+    <row r="274"/>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
@@ -44540,12 +44978,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -45778,12 +46216,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov.</t>
+          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov. || TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Důl Jana Žižky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -45966,12 +46404,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -46102,12 +46540,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Teplice = TJ Sklo Union Teplice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Sklo Union** = sklarsky koncern (drive Sklarny Teplice, dnes AGC - Asahi Glass Company). city Teplice.</t>
+          <t>Teplice = TJ Sklo Union Teplice (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Sklo Union** = sklarsky koncern (drive Sklarny Teplice, dnes AGC - Asahi Glass Company). city Teplice. || TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Sklo Union Teplice</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -46149,12 +46587,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -46536,6 +46974,7 @@
         </is>
       </c>
     </row>
+    <row r="325"/>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
@@ -46784,12 +47223,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -49726,6 +50165,7 @@
         </is>
       </c>
     </row>
+    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -49848,12 +50288,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -50310,12 +50750,12 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou = TJ RH Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **RH** = Ruda hvezda (SNB). Patterns: Žďas Žďár nL Sázavou (strojny) + RH Žďár (policejni klub). city Žďár nad Sázavou.</t>
+          <t>Žďár nad Sázavou = TJ RH Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **RH** = Ruda hvezda (SNB). Patterns: Žďas Žďár nL Sázavou (strojny) + RH Žďár (policejni klub). city Žďár nad Sázavou. || TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>RH Žďár</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -51380,12 +51820,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -52272,6 +52712,7 @@
         </is>
       </c>
     </row>
+    <row r="455"/>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
@@ -52426,12 +52867,12 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>Poruba = TJ Poruba (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). HC Poruba - dnes 2.liga. POZN: 2011 sem prestehovala 2.liga licence z Ceske Lipy. city Poruba.</t>
+          <t>Poruba = TJ Poruba (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). HC Poruba - dnes 2.liga. POZN: 2011 sem prestehovala 2.liga licence z Ceske Lipy. city Poruba. || TBD: city 'Poruba' → 'HM Ostrava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Poruba</t>
+          <t>HM Ostrava</t>
         </is>
       </c>
     </row>
@@ -52515,12 +52956,12 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ VP Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **VP** = Válcovny plechu (pobocka Třinec). city Frýdek-Místek. || TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>VP Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -52557,12 +52998,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -52641,12 +53082,12 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -52814,12 +53255,12 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm.</t>
+          <t>Frenštát pod Radhoštěm = TJ MEZ Frenštát (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Novy Jicin). **MEZ Frenštát** = Moravské elektrotechnické závody (pobocka). city Frenštát pod Radhoštěm. || TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>MEZ Frenštát</t>
+          <t>Frenštát pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -54509,6 +54950,7 @@
         </is>
       </c>
     </row>
+    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
@@ -54621,12 +55063,12 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom.</t>
+          <t>Krizovany nad Dudváhom = TJ Družstevník Krizovany nad Dudváhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trnavsky kraj (okres Trnava). city Krizovany nad Dudváhom. || TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>Družstevník Krizovany nad Dudváhom</t>
+          <t>Krizovany nad Dudváhom</t>
         </is>
       </c>
     </row>
@@ -55914,11 +56356,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -55963,21 +56405,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0035</t>
+          <t>CLUB_S1978_79_0009</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0035 'ŽS Spišská Nová Ves' prev→CLUB_S1977_78_0032 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -55985,21 +56425,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0041</t>
+          <t>CLUB_S1978_79_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0041 'TJ Baník Sokolov' prev→CLUB_S1977_78_0039 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -56007,21 +56445,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0084</t>
+          <t>CLUB_S1978_79_0017</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0084 'TJ Skloobal Nemšová' prev→CLUB_S1977_78_0508 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -56029,21 +56465,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0187</t>
+          <t>CLUB_S1978_79_0029</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0187 'Sokol Záluží (BER)' prev→CLUB_S1977_78_0149 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -56051,21 +56485,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0432</t>
+          <t>CLUB_S1978_79_0032</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0432 'Rájec – Jestřebí' prev→CLUB_S1977_78_0430 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -56073,21 +56505,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0025</t>
+          <t>CLUB_S1978_79_0035</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0025 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -56095,21 +56525,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0026</t>
+          <t>CLUB_S1978_79_0035</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0026 fate nekonzist. ['postup', 'sestup'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -56117,21 +56545,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0027</t>
+          <t>CLUB_S1978_79_0041</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0027 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -56139,21 +56565,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0028</t>
+          <t>CLUB_S1978_79_0045</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0028 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -56161,21 +56585,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0103</t>
+          <t>CLUB_S1978_79_0050</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0103 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -56183,21 +56605,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S1978_79_0009</t>
+          <t>CLUB_S1978_79_0051</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1978_79_0009 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -56205,21 +56625,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NODE_S1978_79_0010</t>
+          <t>CLUB_S1978_79_0052</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1978_79_0010 'Kval o I.ČNHL sk. A' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -56227,21 +56645,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NODE_S1978_79_0011</t>
+          <t>CLUB_S1978_79_0056</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1978_79_0011 'Kval o I.ČNHL sk. B' (L25, parent=NODE_S1978_79_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -56249,24 +56665,762 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NODE_S1978_79_0017</t>
+          <t>CLUB_S1978_79_0060</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1978_79_0017 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1978_79_0012) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0066</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0068</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0070</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0084</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0113</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0133</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0165</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0185</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0187</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0191</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0196</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0202</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0202</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0215</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0220</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0224</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0226</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0258</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0282</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0311</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0315</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0318</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0319</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0335</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0338</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0399</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0403</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0414</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0425</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0432</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0440</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0465</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Poruba' → 'HM Ostrava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0467</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0468</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0470</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0474</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1978_79_0516</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23350,7 +23350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23400,7 +23400,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -23412,7 +23412,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23424,7 +23424,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23436,7 +23436,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23448,7 +23448,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23460,7 +23460,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23472,7 +23472,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23484,7 +23484,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23496,7 +23496,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23508,7 +23508,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23520,7 +23520,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23532,7 +23532,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23544,7 +23544,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23556,7 +23556,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23568,7 +23568,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23580,7 +23580,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23592,7 +23592,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23604,7 +23604,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23616,7 +23616,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23628,7 +23628,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23640,7 +23640,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -23652,7 +23652,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -23664,7 +23664,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -23688,7 +23688,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23700,7 +23700,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23712,7 +23712,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -23724,7 +23724,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23736,7 +23736,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23748,7 +23748,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23760,7 +23760,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23772,7 +23772,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23784,7 +23784,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -23796,7 +23796,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -23808,7 +23808,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -23820,7 +23820,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23832,7 +23832,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -23844,7 +23844,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -23856,7 +23856,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23868,7 +23868,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -23880,130 +23880,10 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Poruba' → 'HM Ostrava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24020,7 +23900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24079,6 +23959,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24121,6 +24006,11 @@
           <t>12 týmů, jeden stůl. Mistr: Slovan CHZJD Bratislava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24210,6 +24100,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK). Kvalifikace o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24252,6 +24147,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24294,6 +24194,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24336,6 +24241,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24378,6 +24288,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24420,6 +24335,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24462,6 +24382,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0014</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24588,6 +24513,11 @@
           <t>II.ČNHL: 3 skupiny po 8. Nově založená soutěž.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0009</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24630,6 +24560,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0010</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24672,6 +24607,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0011</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24714,6 +24654,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0012</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24756,6 +24701,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0013</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24798,6 +24748,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0014</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24840,6 +24795,11 @@
           <t>Divize pouze na Slovensku (v Česku zrušena). 2 skupiny.</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0015</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24882,6 +24842,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0016</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24924,6 +24889,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0017</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25055,6 +25025,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0021</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25181,6 +25156,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0024</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25223,6 +25203,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25265,6 +25250,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0026</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25307,6 +25297,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0027</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25433,6 +25428,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0029</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -25475,6 +25475,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0030</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -25517,6 +25522,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0031</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -25559,6 +25569,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0032</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -25601,6 +25616,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0033</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -25695,6 +25715,11 @@
           <t>kvalifikace o II.třídu (přeborníci okresů)</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0035</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -25737,6 +25762,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0036</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -25821,6 +25851,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0038</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25905,6 +25940,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0040</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -25947,6 +25987,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0041</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25989,6 +26034,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0042</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -26031,6 +26081,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0043</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -26073,6 +26128,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0044</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26115,6 +26175,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0045</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -26157,6 +26222,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0046</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -26199,6 +26269,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0047</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26246,6 +26321,11 @@
           <t>o postup do KP</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0048</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -26335,6 +26415,11 @@
           <t>kvalifikace o II.třídu</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0049</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -26377,6 +26462,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0050</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -26419,6 +26509,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -26587,6 +26682,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0052</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26629,6 +26729,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0053</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -26671,6 +26776,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0054</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -26713,6 +26823,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0055</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -26760,6 +26875,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0056</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26802,6 +26922,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0057</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -26844,6 +26969,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0058</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -26928,6 +27058,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0063</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26970,6 +27105,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0064</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -27012,6 +27152,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0065</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -27143,6 +27288,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0067</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -27185,6 +27335,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0068</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -27358,6 +27513,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0073</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -27400,6 +27560,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0074</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -27442,6 +27607,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0075</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -27484,6 +27654,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0076</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27526,6 +27701,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0077</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27914,6 +28094,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0084</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -27956,6 +28141,11 @@
           <t>Kontejner L60</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0085</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28122,6 +28312,11 @@
       <c r="J96" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1977_78_0086</t>
         </is>
       </c>
     </row>
@@ -33451,12 +33646,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33802,12 +33997,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -34432,12 +34627,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -35534,12 +35729,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -35833,12 +36028,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -41449,12 +41644,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -50288,12 +50483,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -52867,12 +53062,12 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>Poruba = TJ Poruba (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). HC Poruba - dnes 2.liga. POZN: 2011 sem prestehovala 2.liga licence z Ceske Lipy. city Poruba. || TBD: city 'Poruba' → 'HM Ostrava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Poruba = TJ Poruba (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (mestska cast Ostravy). HC Poruba - dnes 2.liga. POZN: 2011 sem prestehovala 2.liga licence z Ceske Lipy. city Poruba.</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>HM Ostrava</t>
+          <t>Poruba</t>
         </is>
       </c>
     </row>
@@ -52998,12 +53193,12 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -53082,12 +53277,12 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -56356,7 +56551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56410,12 +56605,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0009</t>
+          <t>CLUB_S1978_79_0015</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56430,12 +56625,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0015</t>
+          <t>CLUB_S1978_79_0029</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56450,12 +56645,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0017</t>
+          <t>CLUB_S1978_79_0035</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56470,12 +56665,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0029</t>
+          <t>CLUB_S1978_79_0035</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56490,12 +56685,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0032</t>
+          <t>CLUB_S1978_79_0041</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56510,12 +56705,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0035</t>
+          <t>CLUB_S1978_79_0045</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56530,12 +56725,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0035</t>
+          <t>CLUB_S1978_79_0050</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56550,12 +56745,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0041</t>
+          <t>CLUB_S1978_79_0051</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56570,12 +56765,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0045</t>
+          <t>CLUB_S1978_79_0052</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56590,12 +56785,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0050</t>
+          <t>CLUB_S1978_79_0056</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56610,12 +56805,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0051</t>
+          <t>CLUB_S1978_79_0066</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56630,12 +56825,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0052</t>
+          <t>CLUB_S1978_79_0070</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56650,12 +56845,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0056</t>
+          <t>CLUB_S1978_79_0084</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56670,12 +56865,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0060</t>
+          <t>CLUB_S1978_79_0113</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56690,12 +56885,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0066</t>
+          <t>CLUB_S1978_79_0133</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56710,12 +56905,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0068</t>
+          <t>CLUB_S1978_79_0165</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56730,12 +56925,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0070</t>
+          <t>CLUB_S1978_79_0185</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56750,12 +56945,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0084</t>
+          <t>CLUB_S1978_79_0187</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56770,12 +56965,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0113</t>
+          <t>CLUB_S1978_79_0191</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56790,12 +56985,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0133</t>
+          <t>CLUB_S1978_79_0196</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56810,12 +57005,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0165</t>
+          <t>CLUB_S1978_79_0202</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56830,12 +57025,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0185</t>
+          <t>CLUB_S1978_79_0215</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56850,12 +57045,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0187</t>
+          <t>CLUB_S1978_79_0220</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56870,7 +57065,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0191</t>
+          <t>CLUB_S1978_79_0224</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -56890,12 +57085,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0196</t>
+          <t>CLUB_S1978_79_0226</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -56910,12 +57105,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0202</t>
+          <t>CLUB_S1978_79_0258</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56930,12 +57125,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0202</t>
+          <t>CLUB_S1978_79_0282</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56950,12 +57145,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0215</t>
+          <t>CLUB_S1978_79_0311</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56970,12 +57165,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0220</t>
+          <t>CLUB_S1978_79_0315</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56990,12 +57185,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0224</t>
+          <t>CLUB_S1978_79_0318</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57010,12 +57205,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0226</t>
+          <t>CLUB_S1978_79_0319</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57030,12 +57225,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0258</t>
+          <t>CLUB_S1978_79_0335</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57050,12 +57245,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0282</t>
+          <t>CLUB_S1978_79_0338</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -57070,12 +57265,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0311</t>
+          <t>CLUB_S1978_79_0399</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57090,12 +57285,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0315</t>
+          <t>CLUB_S1978_79_0414</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57110,12 +57305,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0318</t>
+          <t>CLUB_S1978_79_0425</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -57130,12 +57325,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0319</t>
+          <t>CLUB_S1978_79_0432</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57150,12 +57345,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0335</t>
+          <t>CLUB_S1978_79_0440</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57170,12 +57365,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0338</t>
+          <t>CLUB_S1978_79_0467</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57190,12 +57385,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0399</t>
+          <t>CLUB_S1978_79_0474</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57210,217 +57405,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1978_79_0403</t>
+          <t>CLUB_S1978_79_0516</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0414</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0425</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0432</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0440</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0465</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Poruba' → 'HM Ostrava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0467</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0468</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0470</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0474</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1978_79_0516</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F52"/>
+  <autoFilter ref="A1:F42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -23350,7 +23350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23398,57 +23398,82 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0022</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] nikdo nepostoupil</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] nikdo nepostoupil</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[club-fate] Vzhledem k reorganizaci soutěží z krajských přeborů nikdo nepostoupil.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] nikdo nepostoupil</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -23460,7 +23485,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -23472,7 +23497,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0032 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -23484,7 +23509,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -23496,7 +23521,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0039 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23508,7 +23533,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23520,7 +23545,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -23532,7 +23557,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -23544,7 +23569,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -23556,7 +23581,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -23568,7 +23593,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23580,7 +23605,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23592,7 +23617,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1977_78_0508 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23604,7 +23629,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23616,7 +23641,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23628,7 +23653,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23640,7 +23665,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Metaz Týnec nad Labem' → 'Týnec nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -23652,7 +23677,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0149 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -23676,7 +23701,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -23688,7 +23713,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23700,7 +23725,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23712,7 +23737,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -23724,7 +23749,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23736,7 +23761,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23748,7 +23773,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23760,7 +23785,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -23772,7 +23797,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23784,7 +23809,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -23796,7 +23821,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sklo Union Teplice' → 'Teplice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -23808,7 +23833,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -23820,7 +23845,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23832,7 +23857,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -23844,7 +23869,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -23856,7 +23881,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RH Žďár' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23868,7 +23893,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -23880,10 +23905,58 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1977_78_0430 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VP Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'MEZ Frenštát' → 'Frenštát pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Družstevník Krizovany nad Dudváhom' → 'Krizovany nad Dudváhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -62376,7 +62449,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Krajské přebory – vítězové / nikdo nepostoupil</t>
+          <t>Krajské přebory – vítězové</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -62413,7 +62486,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Krajské přebory – vítězové / nikdo nepostoupil / Vzhledem k reorganizaci soutěží z krajských přeborů nikdo nepostoupil.</t>
+          <t>Krajské přebory – vítězové</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -62446,7 +62519,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Krajské přebory – vítězové / nikdo nepostoupil / Vítězové českých a slovenských krajských přeborů zachyceni jen evidenčně; bez postupové vazby.</t>
+          <t>Krajské přebory – vítězové / Vítězové českých a slovenských krajských přeborů zachyceni jen evidenčně; bez postupové vazby.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -37081,7 +37081,6 @@
         </is>
       </c>
     </row>
-    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -37680,7 +37679,6 @@
         </is>
       </c>
     </row>
-    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -41216,7 +41214,6 @@
         </is>
       </c>
     </row>
-    <row r="186"/>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
@@ -45081,7 +45078,6 @@
         </is>
       </c>
     </row>
-    <row r="274"/>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
@@ -47242,7 +47238,6 @@
         </is>
       </c>
     </row>
-    <row r="325"/>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
@@ -50433,7 +50428,6 @@
         </is>
       </c>
     </row>
-    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -52980,7 +52974,6 @@
         </is>
       </c>
     </row>
-    <row r="455"/>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
@@ -55218,7 +55211,6 @@
         </is>
       </c>
     </row>
-    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -23973,7 +23973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24035,6 +24035,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -24314,6 +24314,16 @@
           <t>NODE_S1978_79_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24328,6 +24338,14 @@
         <is>
           <t>NODE_S1977_78_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -24361,6 +24379,8 @@
           <t>NODE_S1978_79_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24375,6 +24395,14 @@
         <is>
           <t>NODE_S1977_78_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -24408,6 +24436,8 @@
           <t>NODE_S1978_79_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24422,6 +24452,14 @@
         <is>
           <t>NODE_S1977_78_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -25009,6 +25047,8 @@
           <t>NODE_S1978_79_0018</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25023,6 +25063,14 @@
         <is>
           <t>Prešov – Povážska Bystrica 3:0. 1. a 3. utkání doma.</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -25459,6 +25507,8 @@
           <t>NODE_S1978_79_0026</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25468,6 +25518,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -26107,6 +26165,12 @@
           <t>NODE_S1978_79_0043</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0047</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26121,6 +26185,14 @@
         <is>
           <t>NODE_S1977_78_0042</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -26201,6 +26273,8 @@
           <t>NODE_S1978_79_0043</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26215,6 +26289,14 @@
         <is>
           <t>NODE_S1977_78_0044</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -26441,6 +26523,8 @@
           <t>NODE_S1978_79_0043</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26450,6 +26534,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -26629,6 +26721,16 @@
           <t>NODE_S1978_79_0054</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0057</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0058</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26638,6 +26740,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -26671,6 +26781,8 @@
           <t>NODE_S1978_79_0054</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26680,6 +26792,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -26713,6 +26833,8 @@
           <t>NODE_S1978_79_0054</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26722,6 +26844,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -27680,6 +27810,12 @@
           <t>NODE_S1978_79_0077</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0082</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27694,6 +27830,14 @@
         <is>
           <t>NODE_S1977_78_0075</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -27727,6 +27871,12 @@
           <t>NODE_S1978_79_0077</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0082</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27741,6 +27891,14 @@
         <is>
           <t>NODE_S1977_78_0076</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -27821,6 +27979,8 @@
           <t>NODE_S1978_79_0077</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27830,6 +27990,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1.–6. ZČ</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -28261,6 +28429,16 @@
           <t>NODE_S1978_79_0090</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0093</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>NODE_S1978_79_0094</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28270,6 +28448,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -28303,6 +28489,8 @@
           <t>NODE_S1978_79_0090</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28312,6 +28500,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -28345,6 +28541,8 @@
           <t>NODE_S1978_79_0090</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28354,6 +28552,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -28903,6 +29109,8 @@
           <t>REG_SVK</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28912,6 +29120,14 @@
         <is>
           <t>unknown</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="110">

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -720,6 +720,11 @@
           <t>Slovan CHZJD Bratislava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -24379,8 +24384,6 @@
           <t>NODE_S1978_79_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24436,8 +24439,6 @@
           <t>NODE_S1978_79_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25047,8 +25048,6 @@
           <t>NODE_S1978_79_0018</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25507,8 +25506,6 @@
           <t>NODE_S1978_79_0026</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26165,7 +26162,6 @@
           <t>NODE_S1978_79_0043</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>NODE_S1978_79_0047</t>
@@ -26273,8 +26269,6 @@
           <t>NODE_S1978_79_0043</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26523,8 +26517,6 @@
           <t>NODE_S1978_79_0043</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26781,8 +26773,6 @@
           <t>NODE_S1978_79_0054</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26833,8 +26823,6 @@
           <t>NODE_S1978_79_0054</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27810,7 +27798,6 @@
           <t>NODE_S1978_79_0077</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>NODE_S1978_79_0082</t>
@@ -27871,7 +27858,6 @@
           <t>NODE_S1978_79_0077</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>NODE_S1978_79_0082</t>
@@ -27979,8 +27965,6 @@
           <t>NODE_S1978_79_0077</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28489,8 +28473,6 @@
           <t>NODE_S1978_79_0090</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28541,8 +28523,6 @@
           <t>NODE_S1978_79_0090</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29109,8 +29089,6 @@
           <t>REG_SVK</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -56648,7 +56626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56828,6 +56806,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>Doplněna série Dubnica n/V – Plzeň 1:3, finále SVK divize, node_id u I.ČNHL a 30_SVK, vyčištěn KVAL/SYSTEM/CLUBS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Slovan CHZJD Bratislava</t>
         </is>
       </c>
     </row>

--- a/data/S1978_79_FINAL.xlsx
+++ b/data/S1978_79_FINAL.xlsx
@@ -37285,6 +37285,7 @@
         </is>
       </c>
     </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -37883,6 +37884,7 @@
         </is>
       </c>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -41418,6 +41420,7 @@
         </is>
       </c>
     </row>
+    <row r="186"/>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
@@ -45282,6 +45285,7 @@
         </is>
       </c>
     </row>
+    <row r="274"/>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
@@ -47442,6 +47446,7 @@
         </is>
       </c>
     </row>
+    <row r="325"/>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
@@ -50632,6 +50637,7 @@
         </is>
       </c>
     </row>
+    <row r="396"/>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
@@ -53178,6 +53184,7 @@
         </is>
       </c>
     </row>
+    <row r="455"/>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
@@ -55415,6 +55422,7 @@
         </is>
       </c>
     </row>
+    <row r="507"/>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
